--- a/docs/PROJECT_PLAN_AND_CONVENTIONS.xlsx
+++ b/docs/PROJECT_PLAN_AND_CONVENTIONS.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="48" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
@@ -1192,30 +1192,72 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
+          <t>全量执行5大建议与爬取：本土测量图库、日本刻印字典、转接件BOM、打样模板、跨境爆款兼容榜</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>自主闭环</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>用户全面落地指令</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>assets/img/{indigenous,tools}/, content/catalog/*.json, 5大新页面</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>阶段六：长期体系与文件规范</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
           <t>持续运行 npm test 自动化测试并保持 PR #3 开启</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>自主闭环</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>项目 CI 与测试规范</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>tests/site.test.mjs (31 checks passed)</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>tests/site.test.mjs (36 checks passed)</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>长期持续</t>
         </is>

--- a/docs/PROJECT_PLAN_AND_CONVENTIONS.xlsx
+++ b/docs/PROJECT_PLAN_AND_CONVENTIONS.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="工程执行总计划" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="文件命名与目录体系规范" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="5大工业板块与Retrofit基准" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="01_工程执行总计划" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_文件命名与目录体系规范" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_5大工业板块与Retrofit基准" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,14 +487,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
@@ -552,7 +552,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>WBS-01.0</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -594,7 +594,7 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>WBS-01.1</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -636,7 +636,7 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>WBS-01.2</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>docs/METHODOLOGY_AND_CONTEXT_MEMORY.md</t>
+          <t>docs/01_METHODOLOGY_AND_CONTEXT_MEMORY.md</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>WBS-02.0</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -720,7 +720,7 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>WBS-02.1</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>WBS-02.2</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>大号标签 + 动态样本数量显式绑定 (32/4/10/6/10/2)</t>
+          <t>大号标签 + 动态样本数量显式绑定 (38款: 6/8/10/10/4)</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>WBS-02.3</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>3 大强相关 Retrofit 锁型确立为各板块横向 Block-Hero 大主图入口</t>
+          <t>纯 5 大区域图片画廊入口门户重构 (Pure Gallery Theme)</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>ANSI Deadbolt, Euro 18252, Lockwood 001</t>
+          <t>用户纯图化指示</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>assets/img/hero/*.jpg, build.mjs</t>
+          <t>build.mjs, site.css</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -846,7 +846,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>WBS-03.0</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>30 张 real 图 + 30 张 SVG 原理图</t>
+          <t>38 张 real 图 + 30 张 SVG 原理图</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -888,7 +888,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>WBS-03.1</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -930,7 +930,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>WBS-04.0</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -972,7 +972,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>WBS-04.1</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>前端表单改造为单行直接提交 + 工单号生成 + 剪贴板复制兜底</t>
+          <t>前端表单彻底轻量化为单行输入框 + 提交建议 + 回车 Enter 支持</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>用户交互体验指导</t>
+          <t>用户极简交互指导</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>assets/js/feedback.js, src/layout.mjs</t>
+          <t>src/layout.mjs, feedback.js</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>WBS-05.0</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1056,7 +1056,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>WBS-05.1</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1098,7 +1098,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>WBS-05.2</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>首页上线全球主流改装锁（Nuki/August/SwitchBot/Aqara）对标表格</t>
+          <t>上线日本刻印字典、转接件BOM、开孔打样模板、爆款排行</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>海外社区极限实测数据</t>
+          <t>用户 5 大建议全量落地</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>content/catalog/smart-lock-benchmarks.json</t>
+          <t>content/catalog/*.json, 4 大新页面</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1140,59 +1140,59 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>WBS-06.0</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>阶段六：长期体系与文件规范</t>
+          <t>阶段六：自主进化循环机制</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>出台标准化工程计划模板与全套文件命名规范 Excel</t>
+          <t>部署 10 分钟连续自主优化守护进程 (Daemon Mode)</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>自主闭环</t>
+          <t>自主循环</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>用户最新指令</t>
+          <t>用户持续进化指令</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>docs/PROJECT_PLAN_AND_CONVENTIONS.xlsx</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>已完成</t>
+          <t>tools/runner-10m.py</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>进行中</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>持续常驻</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>WBS-06.1</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>阶段六：长期体系与文件规范</t>
+          <t>阶段六：自主进化循环机制</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>全量执行5大建议与爬取：本土测量图库、日本刻印字典、转接件BOM、打样模板、跨境爆款兼容榜</t>
+          <t>标准化带序号文件规范与工程索引多工作表 Excel</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>用户全面落地指令</t>
+          <t>全套序列号规范</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>assets/img/{indigenous,tools}/, content/catalog/*.json, 5大新页面</t>
+          <t>docs/02_PROJECT_PLAN_AND_CONVENTIONS.xlsx</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -1224,12 +1224,12 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>WBS-06.2</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>阶段六：长期体系与文件规范</t>
+          <t>阶段六：自主进化循环机制</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1274,20 +1274,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GlobalLockSummary 工程文件分类体系与命名规则 (Standard Conventions)</t>
+          <t>GlobalLockSummary 工程文件分类体系与带序列号命名规则 (Standard Conventions)</t>
         </is>
       </c>
     </row>
@@ -1295,268 +1296,318 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>层级编号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>层级分类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>目录物理路径</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>文件命名规则 / 格式模板</t>
-        </is>
-      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>说明与示例</t>
+          <t>带序号文件命名规则 / 格式模板</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>典型实例</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>强制约束原则</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>CAT-01</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>1. 结构化数据库</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>content/catalog/</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>*.json (纯小写横杠 kebab-case)</t>
-        </is>
-      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>gallery.json, field-issues.json, smart-lock-benchmarks.json</t>
+          <t>{序号}_{kebab-case}.json</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>01_gallery.json, 02_field-issues.json, 03_adapters-bom.json</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
           <t>纯数据定义，严禁嵌入可执行 JS 逻辑；必须支持双语 zh/en 字段</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>CAT-02</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>2. 锁族单项参数</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>content/catalog/lock-families/</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>{family-id}.json</t>
-        </is>
-      </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>us-deadbolt.json, au-deadlatch.json, euro-cylinder-mortise.json</t>
+          <t>{序号}_{family-id}.json</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>01_us-deadbolt.json, 02_au-deadlatch.json, 03_euro-cylinder.json</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>ID 必须为全局唯一稳定标识，严禁随意改名破坏外部链接与机读引用</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>PAG-03</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>3. 双语静态页面</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>content/pages/{zh,en}/</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>{slug}.md (小写横杠)</t>
-        </is>
-      </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>index.md, retrofit.md, field-issues.md, identify.md</t>
+          <t>{序号}_{slug}.md (小写横杠)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
+          <t>01_index.md, 02_adapters.md, 03_field-issues.md</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
           <t>以 Markdown 编写，头部携带 FrontMatter (title, description)，必须中英成对存在</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>IMG-04</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>4. 真实安装实物图</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>assets/img/gallery/</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>{region}_{model}_real.{ext}</t>
-        </is>
-      </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>us-27_real.jpg, au-11_real.jpg, sg-01_real.jpg</t>
+          <t>{序号}_{region}_{model}_real.{ext}</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
+          <t>01_us-27_real.jpg, 02_au-11_real.jpg, 03_sg-01_real.jpg</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>必须为门上实物照片；图片宽度统一切割压缩至 &lt;= 1000px，保留清晰度控制体积</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>DIA-05</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>5. 传动受力原理图</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>assets/img/diagrams/</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>{region}_{model}_schematic.svg</t>
-        </is>
-      </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>US-27_schematic.svg, AU-11_schematic.svg, EU-19_schematic.svg</t>
+          <t>{序号}_{region}_{model}_schematic.svg</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
+          <t>01_US-27_schematic.svg, 02_AU-11_schematic.svg</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
           <t>必须为矢量 SVG；统一标明内侧电机、锁体、方轴与联动箭头路线</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>HER-06</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>6. 板块大主图</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>assets/img/hero/</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>hero-{region}-{model}.{ext}</t>
-        </is>
-      </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>hero-na-deadbolt.jpg, hero-europe-eurocylinder.jpg</t>
+          <t>{序号}_hero-{region}-{model}.{ext}</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
+          <t>01_hero-na-deadbolt.jpg, 02_hero-europe-eurocylinder.jpg</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
           <t>用于 5 大板块顶级入口展示的大号横向代表图，长宽比控制在 16:10</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>FUN-07</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>7. 服务端无服务接口</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>functions/api/</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>{service-name}.js</t>
-        </is>
-      </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>functions/api/feedback.js</t>
+          <t>{序号}_{service-name}.js</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
+          <t>01_feedback.js</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
           <t>Cloudflare Pages Functions 接口；严禁将任何 Webhook/API Key 提交至 Git</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>TLS-08</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>8. 自动化与爬取脚本</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>tools/</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>{verb}-{noun}.mjs</t>
-        </is>
-      </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>tools/fetch-field-issues.mjs, tools/validate-data.mjs</t>
+          <t>{序号}_{verb}-{noun}.mjs|py</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Node.js ESM 脚本；用于数据自动拉取、清洗转换与引用完整性校验</t>
+          <t>01_fetch-field-issues.mjs, 02_generate-project-excel.py</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Node.js ESM 或 Python3 脚本；用于数据自动拉取、清洗转换与引用完整性校验</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>DOC-09</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>9. 长期记忆与文档</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>docs/</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>*.md / *.xlsx (大写下划线或标准名)</t>
-        </is>
-      </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>docs/METHODOLOGY_AND_CONTEXT_MEMORY.md, docs/PROJECT_PLAN_AND_CONVENTIONS.xlsx</t>
+          <t>{序号}_{NAME}.md / *.xlsx</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>01_METHODOLOGY_MEMORY.md, 02_PROJECT_PLAN.xlsx, 03_MASTER_INDEX.xlsx</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>永久固化用户沟通指令、演进决策与全景规划，防跨会话失忆</t>
         </is>
@@ -1573,16 +1624,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -1596,35 +1648,40 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>板块序号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>板块代码</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>工业板块名称</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>涵盖重点国家</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>遵循主流五金标准</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>核心代表机械锁族</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Retrofit 强相关度</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>核心改装成败死穴 (Engineering Bottleneck)</t>
         </is>
@@ -1633,35 +1690,40 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>DIV-01</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>na</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>🇺🇸 北美标准板块 (Americas)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>美国、加拿大、墨西哥</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>ANSI/BHMA A156.36 / A156.2</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>单缸插销死锁 (Deadbolt / Schlage B60)</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>⭐⭐⭐ 极强相关 (基准)</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>木门受潮下沉或防风条弹性将门向外推，导致插销与扣板卡阻 (Deadbolt Jam)</t>
         </is>
@@ -1670,35 +1732,40 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>DIV-02</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
           <t>europe5</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>🇪🇺 欧陆五国板块 (Continental Europe)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>德国、法国、意大利、西班牙、荷兰</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>DIN 18251 / 18252, EN 12209</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>欧标槽型双锁芯 (Euro Profile DIN 18252)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>⭐⭐⭐ 极强相关 (基准)</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>内侧常插钥匙时，锁芯必须具备 DIN 18252 BS 双向应急离合认证，否则断电造成彻底反锁</t>
         </is>
@@ -1707,35 +1774,40 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>DIV-03</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
           <t>uk-anz</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>🇦🇺🇬🇧 澳洲与英国板块 (Pacific &amp; UK)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>澳大利亚、新西兰、英国、爱尔兰</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>AS 4174 (澳标), BS 3621 (英标)</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>澳式外装夜锁与双扣锁 (Lockwood 001/355)</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>⭐⭐⭐ 极强相关 (基准)</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>辅助锁舌 (Auxiliary Latch) 必须完全压入门框扣板，否则旋钮转动主舌并未死锁 (假安全)</t>
         </is>
@@ -1744,35 +1816,40 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>DIV-04</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
           <t>sea</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>🇸🇬 东南亚与东亚板块 (Asia-Pacific)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>新加坡、马来西亚、泰国、越南、韩国</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>SS 312, SCDF 逃生规范, KS</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>新加坡 HDB 铁闸锁与推拉式插芯锁</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>⭐⭐ 强相关 (边界)</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>组屋双门外闸与内木门净距 &lt;80mm，智能锁厚度超过 35mm 即发生把手致命撞击</t>
         </is>
@@ -1781,35 +1858,40 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>DIV-05</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
           <t>latam</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>🌎 拉美新兴板块 (Latin America)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>巴西、智利、秘鲁、哥伦比亚、阿根廷</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>ABNT NBR 14913, ODIS 体系</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>拉美 ABNT 40/45mm 极窄背距插芯把手锁</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>⭐⭐ 强相关 (边界)</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>背距极窄且门扇仅 30mm 厚，电机底座稍宽即撞击门框防风条</t>
         </is>
